--- a/03_Outputs/all/idx7_gini_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx7_gini_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>-0.7071067811865472</v>
+        <v>-0.7071067811865477</v>
       </c>
       <c r="D2">
-        <v>0.4999999999999998</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="E2">
         <v>50</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.7071067811865479</v>
+        <v>-0.7071067811865474</v>
       </c>
       <c r="D3">
-        <v>0.5000000000000002</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="E3">
         <v>50</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.7071067811865479</v>
+        <v>-0.7071067811865474</v>
       </c>
       <c r="D4">
-        <v>0.5000000000000002</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="E4">
         <v>50</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.7071067811865472</v>
+        <v>0.7071067811865477</v>
       </c>
       <c r="D5">
-        <v>0.4999999999999998</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="E5">
         <v>50</v>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1413061513338738</v>
+        <v>0.1413061513338739</v>
       </c>
     </row>
   </sheetData>
@@ -540,11 +540,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gini ingresos laborales</t>
+          <t>Gini ingresos de hogares</t>
         </is>
       </c>
       <c r="B2">
-        <v>-0.7071067811865479</v>
+        <v>-0.7071067811865477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -555,11 +555,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gini ingresos de hogares</t>
+          <t>Gini ingresos laborales</t>
         </is>
       </c>
       <c r="B3">
-        <v>-0.7071067811865472</v>
+        <v>-0.7071067811865474</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -597,30 +597,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gini ingresos de hogares</t>
+          <t>Gini ingresos laborales</t>
         </is>
       </c>
       <c r="B2">
-        <v>-0.7071067811865479</v>
+        <v>0.7071067811865477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gini ingresos laborales</t>
+          <t>Gini ingresos de hogares</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.7071067811865472</v>
+        <v>-0.7071067811865474</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
     </row>
